--- a/polls/010_digital_content_accessibility_poll_form--polls.xlsx
+++ b/polls/010_digital_content_accessibility_poll_form--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -857,8 +857,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -886,12 +886,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_following_text_navigation'}</t>
+          <t>difficulty_following_text_navigation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty following text navigation'}</t>
+          <t>Difficulty following text navigation</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_using_a_keyboard_or_mouse'}</t>
+          <t>difficulty_using_a_keyboard_or_mouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty using a keyboard or mouse'}</t>
+          <t>Difficulty using a keyboard or mouse</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_following_text_navigation'}</t>
+          <t>difficulty_following_text_navigation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty following text navigation'}</t>
+          <t>Difficulty following text navigation</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_using_a_keyboard_or_mouse'}</t>
+          <t>difficulty_using_a_keyboard_or_mouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty using a keyboard or mouse'}</t>
+          <t>Difficulty using a keyboard or mouse</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_using_a_keyboard_or_mouse'}</t>
+          <t>difficulty_using_a_keyboard_or_mouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty using a keyboard or mouse'}</t>
+          <t>Difficulty using a keyboard or mouse</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'difficulty_following_text_navigation'}</t>
+          <t>difficulty_following_text_navigation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Difficulty following text navigation'}</t>
+          <t>Difficulty following text navigation</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not very likely'}</t>
+          <t>Not very likely</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'likely'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Likely'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not applicable'}</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'not_known'}</t>
+          <t>not_known</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Not known'}</t>
+          <t>Not known</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
